--- a/assets/libreoffice_calc_njc/df47cfc4-b12a-4e1c-89f5-94fda600b12e/Branch_Manager_Lookup.xlsx
+++ b/assets/libreoffice_calc_njc/df47cfc4-b12a-4e1c-89f5-94fda600b12e/Branch_Manager_Lookup.xlsx
@@ -189,8 +189,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -212,158 +216,158 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="str">
+      <c r="C2" s="1" t="str">
         <f aca="false">VLOOKUP(B2,Lookup!$A$1:$B$8,2,0)</f>
         <v>John Smith</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="str">
+      <c r="C3" s="1" t="str">
         <f aca="false">VLOOKUP(B3,Lookup!$A$1:$B$8,2,0)</f>
         <v>Robert Brown</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="str">
+      <c r="C4" s="1" t="str">
         <f aca="false">VLOOKUP(B4,Lookup!$A$1:$B$8,2,0)</f>
         <v>Patricia Davis</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="str">
+      <c r="C5" s="1" t="str">
         <f aca="false">VLOOKUP(B5,Lookup!$A$1:$B$8,2,0)</f>
         <v>John Smith</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="str">
+      <c r="C6" s="1" t="str">
         <f aca="false">VLOOKUP(B6,Lookup!$A$1:$B$8,2,0)</f>
         <v>Michael Wilson</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="str">
+      <c r="C7" s="1" t="str">
         <f aca="false">VLOOKUP(B7,Lookup!$A$1:$B$8,2,0)</f>
         <v>Mary Johnson</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="0" t="str">
+      <c r="C9" s="1" t="str">
         <f aca="false">VLOOKUP(B9,Lookup!$A$1:$B$8,2,0)</f>
         <v>Robert Brown</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="0" t="str">
+      <c r="C10" s="1" t="str">
         <f aca="false">VLOOKUP(B10,Lookup!$A$1:$B$8,2,0)</f>
         <v>Linda Moore</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="0" t="str">
+      <c r="C11" s="1" t="str">
         <f aca="false">VLOOKUP(B11,Lookup!$A$1:$B$8,2,0)</f>
         <v>William Taylor</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="0" t="str">
+      <c r="C12" s="1" t="str">
         <f aca="false">VLOOKUP(B12,Lookup!$A$1:$B$8,2,0)</f>
         <v>John Smith</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="0" t="str">
+      <c r="C13" s="1" t="str">
         <f aca="false">VLOOKUP(B13,Lookup!$A$1:$B$8,2,0)</f>
         <v>Patricia Davis</v>
       </c>
@@ -385,77 +389,77 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
